--- a/db/tablas_procesadas/Detalle_materia.xlsx
+++ b/db/tablas_procesadas/Detalle_materia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD3545C-4436-45C8-BE97-BF60ADEBCC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F085BD5-BEA9-4E8B-AFF9-1148CC8ADABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="1305" windowWidth="28785" windowHeight="15345" xr2:uid="{9645E043-A915-45BA-A74B-6A06D7338E21}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{9645E043-A915-45BA-A74B-6A06D7338E21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="163">
   <si>
     <t>requisito_id</t>
   </si>
@@ -156,9 +156,6 @@
     <t>TC-INC-003</t>
   </si>
   <si>
-    <t>AMC-INC-003</t>
-  </si>
-  <si>
     <t>DI-INC-003</t>
   </si>
   <si>
@@ -448,6 +445,84 @@
   </si>
   <si>
     <t>Orquestal</t>
+  </si>
+  <si>
+    <t>sala_id</t>
+  </si>
+  <si>
+    <t>F-101</t>
+  </si>
+  <si>
+    <t>F-102</t>
+  </si>
+  <si>
+    <t>F-103</t>
+  </si>
+  <si>
+    <t>F-104</t>
+  </si>
+  <si>
+    <t>B-101</t>
+  </si>
+  <si>
+    <t>D-217</t>
+  </si>
+  <si>
+    <t>C-101</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>B-102</t>
+  </si>
+  <si>
+    <t>D-218</t>
+  </si>
+  <si>
+    <t>B-103</t>
+  </si>
+  <si>
+    <t>B-104</t>
+  </si>
+  <si>
+    <t>B-105</t>
+  </si>
+  <si>
+    <t>AM-INC-003</t>
+  </si>
+  <si>
+    <t>B-201</t>
+  </si>
+  <si>
+    <t>B-202</t>
+  </si>
+  <si>
+    <t>B-203</t>
+  </si>
+  <si>
+    <t>E-101</t>
+  </si>
+  <si>
+    <t>A-305</t>
+  </si>
+  <si>
+    <t>B-204</t>
+  </si>
+  <si>
+    <t>B-205</t>
+  </si>
+  <si>
+    <t>A-302</t>
+  </si>
+  <si>
+    <t>A-203</t>
+  </si>
+  <si>
+    <t>A-303</t>
+  </si>
+  <si>
+    <t>A-304</t>
   </si>
 </sst>
 </file>
@@ -503,9 +578,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -543,7 +618,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -649,7 +724,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -791,7 +866,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -799,14 +874,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448362D5-37D8-4059-AA07-93A9D8C72116}">
-  <dimension ref="A1:E151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F151"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -817,2559 +893,3012 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25001</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="D2" t="s">
+        <v>139</v>
       </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25002</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" t="s">
+        <v>138</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25003</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>2</v>
+      <c r="D4" t="s">
+        <v>141</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25004</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>2</v>
+      <c r="D5" t="s">
+        <v>139</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25005</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="D6" t="s">
+        <v>140</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25006</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="D7" t="s">
+        <v>141</v>
       </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25007</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8">
-        <v>2</v>
+      <c r="D8" t="s">
+        <v>138</v>
       </c>
       <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25008</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9">
-        <v>2</v>
+      <c r="D9" t="s">
+        <v>139</v>
       </c>
       <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25009</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10">
-        <v>2</v>
+      <c r="D10" t="s">
+        <v>139</v>
       </c>
       <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25010</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="s">
+        <v>140</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25011</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12">
-        <v>2</v>
+      <c r="D12" t="s">
+        <v>139</v>
       </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25012</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="s">
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25013</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D14">
-        <v>2</v>
+      <c r="D14" t="s">
+        <v>141</v>
       </c>
       <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25014</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="D15">
-        <v>1</v>
+      <c r="D15" t="s">
+        <v>140</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25015</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
-      <c r="D16">
-        <v>2</v>
+      <c r="D16" t="s">
+        <v>139</v>
       </c>
       <c r="E16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25016</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
-        <v>2</v>
+      <c r="D17" t="s">
+        <v>139</v>
       </c>
       <c r="E17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25017</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="D18">
-        <v>2</v>
+      <c r="D18" t="s">
+        <v>138</v>
       </c>
       <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25018</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
-      <c r="D19">
-        <v>2</v>
+      <c r="D19" t="s">
+        <v>141</v>
       </c>
       <c r="E19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25019</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="D20">
-        <v>1</v>
+      <c r="D20" t="s">
+        <v>140</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25020</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="D21">
-        <v>2</v>
+      <c r="D21" t="s">
+        <v>139</v>
       </c>
       <c r="E21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25021</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22">
-        <v>2</v>
+      <c r="D22" t="s">
+        <v>139</v>
       </c>
       <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25022</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
       </c>
-      <c r="D23">
-        <v>1</v>
+      <c r="D23" t="s">
+        <v>138</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25023</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
       </c>
-      <c r="D24">
-        <v>1</v>
+      <c r="D24" t="s">
+        <v>141</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25024</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
-      <c r="D25">
-        <v>1</v>
+      <c r="D25" t="s">
+        <v>140</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25025</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
       </c>
-      <c r="D26">
-        <v>2</v>
+      <c r="D26" t="s">
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25026</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
       </c>
-      <c r="D27">
-        <v>2</v>
+      <c r="D27" t="s">
+        <v>141</v>
       </c>
       <c r="E27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25027</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
-      <c r="D28">
-        <v>2</v>
+      <c r="D28" t="s">
+        <v>139</v>
       </c>
       <c r="E28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25028</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
       </c>
-      <c r="D29">
-        <v>1</v>
+      <c r="D29" t="s">
+        <v>138</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25029</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
       </c>
-      <c r="D30">
-        <v>1</v>
+      <c r="D30" t="s">
+        <v>141</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>25030</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
-      <c r="D31">
-        <v>1</v>
+      <c r="D31" t="s">
+        <v>140</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>25031</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32">
-        <v>2</v>
+      <c r="D32" t="s">
+        <v>139</v>
       </c>
       <c r="E32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>25032</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
       </c>
-      <c r="D33">
-        <v>2</v>
+      <c r="D33" t="s">
+        <v>141</v>
       </c>
       <c r="E33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>25033</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
       </c>
-      <c r="D34">
-        <v>2</v>
+      <c r="D34" t="s">
+        <v>142</v>
       </c>
       <c r="E34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>25034</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="s">
+        <v>142</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>25035</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
       </c>
-      <c r="D36">
-        <v>1</v>
+      <c r="D36" t="s">
+        <v>142</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>25036</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
         <v>24</v>
       </c>
-      <c r="D37">
-        <v>2</v>
+      <c r="D37" t="s">
+        <v>147</v>
       </c>
       <c r="E37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>25037</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
         <v>25</v>
       </c>
-      <c r="D38">
-        <v>1</v>
+      <c r="D38" t="s">
+        <v>143</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>25038</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
       </c>
-      <c r="D39">
-        <v>1</v>
+      <c r="D39" t="s">
+        <v>142</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>25039</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
-      <c r="D40">
-        <v>2</v>
+      <c r="D40" t="s">
+        <v>144</v>
       </c>
       <c r="E40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>25040</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
       </c>
-      <c r="D41">
-        <v>2</v>
+      <c r="D41" t="s">
+        <v>145</v>
       </c>
       <c r="E41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>25041</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
-      <c r="D42">
-        <v>2</v>
+      <c r="D42" t="s">
+        <v>146</v>
       </c>
       <c r="E42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>25042</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
       </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="D43" t="s">
+        <v>146</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>25043</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="D44">
-        <v>1</v>
+      <c r="D44" t="s">
+        <v>146</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>25044</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="D45">
-        <v>2</v>
+      <c r="D45" t="s">
+        <v>147</v>
       </c>
       <c r="E45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>25045</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="D46">
-        <v>1</v>
+      <c r="D46" t="s">
+        <v>143</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>25046</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
         <v>26</v>
       </c>
-      <c r="D47">
-        <v>1</v>
+      <c r="D47" t="s">
+        <v>146</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>25047</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
-      <c r="D48">
-        <v>2</v>
+      <c r="D48" t="s">
+        <v>144</v>
       </c>
       <c r="E48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>25048</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
       </c>
-      <c r="D49">
-        <v>2</v>
+      <c r="D49" t="s">
+        <v>145</v>
       </c>
       <c r="E49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>25049</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
         <v>29</v>
       </c>
-      <c r="D50">
-        <v>2</v>
+      <c r="D50" t="s">
+        <v>148</v>
       </c>
       <c r="E50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>25050</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
         <v>30</v>
       </c>
-      <c r="D51">
-        <v>2</v>
+      <c r="D51" t="s">
+        <v>148</v>
       </c>
       <c r="E51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>25051</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
       </c>
-      <c r="D52">
-        <v>2</v>
+      <c r="D52" t="s">
+        <v>148</v>
       </c>
       <c r="E52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>25052</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
       </c>
-      <c r="D53">
-        <v>2</v>
+      <c r="D53" t="s">
+        <v>147</v>
       </c>
       <c r="E53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>25053</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
       </c>
-      <c r="D54">
-        <v>1</v>
+      <c r="D54" t="s">
+        <v>143</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>25054</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
         <v>34</v>
       </c>
-      <c r="D55">
-        <v>1</v>
+      <c r="D55" t="s">
+        <v>148</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>25055</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
         <v>35</v>
       </c>
-      <c r="D56">
-        <v>2</v>
+      <c r="D56" t="s">
+        <v>144</v>
       </c>
       <c r="E56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>25056</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="D57">
-        <v>2</v>
+      <c r="D57" t="s">
+        <v>149</v>
       </c>
       <c r="E57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>25057</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="D58">
-        <v>2</v>
+      <c r="D58" t="s">
+        <v>149</v>
       </c>
       <c r="E58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>25058</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="D59">
-        <v>2</v>
+      <c r="D59" t="s">
+        <v>149</v>
       </c>
       <c r="E59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>25059</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="D60">
-        <v>2</v>
+      <c r="D60" t="s">
+        <v>147</v>
       </c>
       <c r="E60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>25060</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C61" t="s">
         <v>33</v>
       </c>
-      <c r="D61">
-        <v>1</v>
+      <c r="D61" t="s">
+        <v>143</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>25061</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C62" t="s">
         <v>34</v>
       </c>
-      <c r="D62">
-        <v>1</v>
+      <c r="D62" t="s">
+        <v>149</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>25062</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63" t="s">
         <v>35</v>
       </c>
-      <c r="D63">
-        <v>2</v>
+      <c r="D63" t="s">
+        <v>144</v>
       </c>
       <c r="E63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>25063</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
       </c>
-      <c r="D64">
-        <v>2</v>
+      <c r="D64" t="s">
+        <v>150</v>
       </c>
       <c r="E64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>25064</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
         <v>37</v>
       </c>
-      <c r="D65">
-        <v>2</v>
+      <c r="D65" t="s">
+        <v>150</v>
       </c>
       <c r="E65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>25065</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C66" t="s">
         <v>38</v>
       </c>
-      <c r="D66">
-        <v>2</v>
+      <c r="D66" t="s">
+        <v>150</v>
       </c>
       <c r="E66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>25066</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
         <v>39</v>
       </c>
-      <c r="D67">
-        <v>2</v>
+      <c r="D67" t="s">
+        <v>147</v>
       </c>
       <c r="E67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>25067</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>40</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
+        <v>151</v>
+      </c>
+      <c r="D68" t="s">
+        <v>143</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>25068</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>41</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="D69" t="s">
+        <v>150</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>25069</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>42</v>
-      </c>
-      <c r="D70">
-        <v>2</v>
+        <v>41</v>
+      </c>
+      <c r="D70" t="s">
+        <v>150</v>
       </c>
       <c r="E70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>25071</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
-      </c>
-      <c r="D71">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="D71" t="s">
+        <v>152</v>
       </c>
       <c r="E71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>25072</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72">
-        <v>2</v>
+        <v>43</v>
+      </c>
+      <c r="D72" t="s">
+        <v>152</v>
       </c>
       <c r="E72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>25073</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73">
-        <v>2</v>
+        <v>44</v>
+      </c>
+      <c r="D73" t="s">
+        <v>152</v>
       </c>
       <c r="E73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>25074</v>
       </c>
       <c r="B74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>46</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="D74" t="s">
+        <v>143</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>25075</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>47</v>
-      </c>
-      <c r="D75">
+        <v>46</v>
+      </c>
+      <c r="D75" t="s">
+        <v>144</v>
+      </c>
+      <c r="E75">
         <v>3</v>
       </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>25077</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>48</v>
-      </c>
-      <c r="D76">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="D76" t="s">
+        <v>155</v>
       </c>
       <c r="E76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>25078</v>
       </c>
       <c r="B77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>49</v>
-      </c>
-      <c r="D77">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="D77" t="s">
+        <v>153</v>
       </c>
       <c r="E77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>25079</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>50</v>
-      </c>
-      <c r="D78">
-        <v>2</v>
+        <v>49</v>
+      </c>
+      <c r="D78" t="s">
+        <v>153</v>
       </c>
       <c r="E78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>25080</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
-      </c>
-      <c r="D79">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="D79" t="s">
+        <v>153</v>
       </c>
       <c r="E79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>25081</v>
       </c>
       <c r="B80" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>143</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>25082</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
-      </c>
-      <c r="D81">
+        <v>52</v>
+      </c>
+      <c r="D81" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81">
         <v>3</v>
       </c>
-      <c r="E81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>25084</v>
       </c>
       <c r="B82" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C82" t="s">
-        <v>54</v>
-      </c>
-      <c r="D82">
-        <v>2</v>
+        <v>53</v>
+      </c>
+      <c r="D82" t="s">
+        <v>155</v>
       </c>
       <c r="E82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>25085</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C83" t="s">
-        <v>55</v>
-      </c>
-      <c r="D83">
-        <v>2</v>
+        <v>54</v>
+      </c>
+      <c r="D83" t="s">
+        <v>154</v>
       </c>
       <c r="E83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>25086</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
-      </c>
-      <c r="D84">
-        <v>2</v>
+        <v>55</v>
+      </c>
+      <c r="D84" t="s">
+        <v>154</v>
       </c>
       <c r="E84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>25087</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C85" t="s">
-        <v>57</v>
-      </c>
-      <c r="D85">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="D85" t="s">
+        <v>154</v>
       </c>
       <c r="E85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>25088</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
-      </c>
-      <c r="D86">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="D86" t="s">
+        <v>156</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>25089</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>59</v>
-      </c>
-      <c r="D87">
+        <v>58</v>
+      </c>
+      <c r="D87" t="s">
+        <v>144</v>
+      </c>
+      <c r="E87">
         <v>3</v>
       </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>25091</v>
       </c>
       <c r="B88" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88">
-        <v>2</v>
+        <v>59</v>
+      </c>
+      <c r="D88" t="s">
+        <v>155</v>
       </c>
       <c r="E88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>25092</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
-        <v>61</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="D89" t="s">
+        <v>157</v>
       </c>
       <c r="E89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>25093</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C90" t="s">
-        <v>62</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="D90" t="s">
+        <v>157</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>25094</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s">
-        <v>63</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="D91" t="s">
+        <v>157</v>
       </c>
       <c r="E91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>25095</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C92" t="s">
-        <v>64</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="D92" t="s">
+        <v>143</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>25096</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93" t="s">
-        <v>65</v>
-      </c>
-      <c r="D93">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="D93" t="s">
+        <v>157</v>
       </c>
       <c r="E93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>25097</v>
       </c>
       <c r="B94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94">
-        <v>2</v>
+        <v>65</v>
+      </c>
+      <c r="D94" t="s">
+        <v>147</v>
       </c>
       <c r="E94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>25098</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C95" t="s">
-        <v>67</v>
-      </c>
-      <c r="D95">
-        <v>2</v>
+        <v>66</v>
+      </c>
+      <c r="D95" t="s">
+        <v>155</v>
       </c>
       <c r="E95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>25100</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="D96" t="s">
+        <v>145</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>25101</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C97" t="s">
-        <v>61</v>
-      </c>
-      <c r="D97">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="D97" t="s">
+        <v>158</v>
       </c>
       <c r="E97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>25102</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>62</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="D98" t="s">
+        <v>158</v>
       </c>
       <c r="E98">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>25103</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s">
-        <v>63</v>
-      </c>
-      <c r="D99">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="D99" t="s">
+        <v>158</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>25104</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C100" t="s">
-        <v>64</v>
-      </c>
-      <c r="D100">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="D100" t="s">
+        <v>143</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>25105</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>65</v>
-      </c>
-      <c r="D101">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="D101" t="s">
+        <v>158</v>
       </c>
       <c r="E101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>25106</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>66</v>
-      </c>
-      <c r="D102">
-        <v>2</v>
+        <v>65</v>
+      </c>
+      <c r="D102" t="s">
+        <v>147</v>
       </c>
       <c r="E102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>25107</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>67</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
+        <v>66</v>
+      </c>
+      <c r="D103" t="s">
+        <v>155</v>
       </c>
       <c r="E103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>25109</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>68</v>
-      </c>
-      <c r="D104">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="D104" t="s">
+        <v>145</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>25110</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C105" t="s">
-        <v>69</v>
-      </c>
-      <c r="D105">
-        <v>2</v>
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>160</v>
       </c>
       <c r="E105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>25111</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>70</v>
-      </c>
-      <c r="D106">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="D106" t="s">
+        <v>160</v>
       </c>
       <c r="E106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>25112</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>71</v>
-      </c>
-      <c r="D107">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="D107" t="s">
+        <v>160</v>
       </c>
       <c r="E107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>25113</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="s">
-        <v>72</v>
-      </c>
-      <c r="D108">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="D108" t="s">
+        <v>160</v>
       </c>
       <c r="E108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>25114</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>73</v>
-      </c>
-      <c r="D109">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="D109" t="s">
+        <v>147</v>
       </c>
       <c r="E109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>25115</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C110" t="s">
-        <v>74</v>
-      </c>
-      <c r="D110">
-        <v>2</v>
+        <v>73</v>
+      </c>
+      <c r="D110" t="s">
+        <v>144</v>
       </c>
       <c r="E110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>25117</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C111" t="s">
-        <v>75</v>
-      </c>
-      <c r="D111">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="D111" t="s">
+        <v>155</v>
       </c>
       <c r="E111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>25118</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>76</v>
-      </c>
-      <c r="D112">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="D112" t="s">
+        <v>159</v>
       </c>
       <c r="E112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>25119</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>77</v>
-      </c>
-      <c r="D113">
-        <v>2</v>
+        <v>76</v>
+      </c>
+      <c r="D113" t="s">
+        <v>159</v>
       </c>
       <c r="E113">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>25120</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C114" t="s">
-        <v>78</v>
-      </c>
-      <c r="D114">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="D114" t="s">
+        <v>159</v>
       </c>
       <c r="E114">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>25121</v>
       </c>
       <c r="B115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C115" t="s">
-        <v>79</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="D115" t="s">
+        <v>159</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>25122</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>80</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="D116" t="s">
+        <v>147</v>
       </c>
       <c r="E116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>25123</v>
       </c>
       <c r="B117" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C117" t="s">
-        <v>81</v>
-      </c>
-      <c r="D117">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="D117" t="s">
+        <v>144</v>
       </c>
       <c r="E117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>25125</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C118" t="s">
-        <v>82</v>
-      </c>
-      <c r="D118">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="D118" t="s">
+        <v>155</v>
       </c>
       <c r="E118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>25126</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C119" t="s">
-        <v>83</v>
-      </c>
-      <c r="D119">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="D119" t="s">
+        <v>161</v>
       </c>
       <c r="E119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>25127</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C120" t="s">
-        <v>84</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
+        <v>83</v>
+      </c>
+      <c r="D120" t="s">
+        <v>161</v>
       </c>
       <c r="E120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>25128</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C121" t="s">
-        <v>85</v>
-      </c>
-      <c r="D121">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="D121" t="s">
+        <v>161</v>
       </c>
       <c r="E121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>25129</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C122" t="s">
-        <v>86</v>
-      </c>
-      <c r="D122">
-        <v>1</v>
+        <v>85</v>
+      </c>
+      <c r="D122" t="s">
+        <v>161</v>
       </c>
       <c r="E122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>25130</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C123" t="s">
-        <v>87</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="D123" t="s">
+        <v>161</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>25131</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C124" t="s">
-        <v>88</v>
-      </c>
-      <c r="D124">
+        <v>87</v>
+      </c>
+      <c r="D124" t="s">
+        <v>144</v>
+      </c>
+      <c r="E124">
         <v>3</v>
       </c>
-      <c r="E124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>25133</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C125" t="s">
-        <v>89</v>
-      </c>
-      <c r="D125">
+        <v>88</v>
+      </c>
+      <c r="D125" t="s">
+        <v>155</v>
+      </c>
+      <c r="E125">
         <v>3</v>
       </c>
-      <c r="E125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>25134</v>
       </c>
       <c r="B126" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C126" t="s">
-        <v>90</v>
-      </c>
-      <c r="D126">
-        <v>2</v>
+        <v>89</v>
+      </c>
+      <c r="D126" t="s">
+        <v>162</v>
       </c>
       <c r="E126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>25135</v>
       </c>
       <c r="B127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C127" t="s">
-        <v>91</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="D127" t="s">
+        <v>162</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>25136</v>
       </c>
       <c r="B128" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C128" t="s">
-        <v>92</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="D128" t="s">
+        <v>162</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>25137</v>
       </c>
       <c r="B129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C129" t="s">
-        <v>93</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="D129" t="s">
+        <v>162</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>25138</v>
       </c>
       <c r="B130" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C130" t="s">
-        <v>94</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="D130" t="s">
+        <v>162</v>
       </c>
       <c r="E130">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>25139</v>
       </c>
       <c r="B131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C131" t="s">
-        <v>95</v>
-      </c>
-      <c r="D131">
+        <v>94</v>
+      </c>
+      <c r="D131" t="s">
+        <v>144</v>
+      </c>
+      <c r="E131">
         <v>3</v>
       </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>25141</v>
       </c>
       <c r="B132" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C132" t="s">
-        <v>96</v>
-      </c>
-      <c r="D132">
+        <v>95</v>
+      </c>
+      <c r="D132" t="s">
+        <v>155</v>
+      </c>
+      <c r="E132">
         <v>3</v>
       </c>
-      <c r="E132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>25142</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C133" t="s">
-        <v>97</v>
-      </c>
-      <c r="D133">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="D133" t="s">
+        <v>156</v>
       </c>
       <c r="E133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>25143</v>
       </c>
       <c r="B134" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C134" t="s">
-        <v>98</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="D134" t="s">
+        <v>156</v>
       </c>
       <c r="E134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>25144</v>
       </c>
       <c r="B135" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C135" t="s">
-        <v>99</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="D135" t="s">
+        <v>156</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>25145</v>
       </c>
       <c r="B136" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C136" t="s">
-        <v>100</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="D136" t="s">
+        <v>156</v>
       </c>
       <c r="E136">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>25146</v>
       </c>
       <c r="B137" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="D137" t="s">
+        <v>156</v>
       </c>
       <c r="E137">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>25147</v>
       </c>
       <c r="B138" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C138" t="s">
-        <v>102</v>
-      </c>
-      <c r="D138">
+        <v>101</v>
+      </c>
+      <c r="D138" t="s">
+        <v>144</v>
+      </c>
+      <c r="E138">
         <v>3</v>
       </c>
-      <c r="E138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>25149</v>
       </c>
       <c r="B139" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
-      </c>
-      <c r="D139">
+        <v>102</v>
+      </c>
+      <c r="D139" t="s">
+        <v>155</v>
+      </c>
+      <c r="E139">
         <v>3</v>
       </c>
-      <c r="E139">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>35001</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C140" t="s">
-        <v>125</v>
-      </c>
-      <c r="D140">
-        <v>2</v>
+        <v>124</v>
+      </c>
+      <c r="D140" t="s">
+        <v>144</v>
       </c>
       <c r="E140">
         <v>2</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>35002</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C141" t="s">
-        <v>126</v>
-      </c>
-      <c r="D141">
-        <v>2</v>
+        <v>125</v>
+      </c>
+      <c r="D141" t="s">
+        <v>142</v>
       </c>
       <c r="E141">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>35003</v>
       </c>
       <c r="B142" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
-      </c>
-      <c r="D142">
-        <v>2</v>
+        <v>126</v>
+      </c>
+      <c r="D142" t="s">
+        <v>149</v>
       </c>
       <c r="E142">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>35004</v>
       </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C143" t="s">
-        <v>128</v>
-      </c>
-      <c r="D143">
-        <v>2</v>
+        <v>127</v>
+      </c>
+      <c r="D143" t="s">
+        <v>144</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>35005</v>
       </c>
       <c r="B144" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C144" t="s">
-        <v>129</v>
-      </c>
-      <c r="D144">
-        <v>2</v>
+        <v>128</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>35006</v>
       </c>
       <c r="B145" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C145" t="s">
-        <v>130</v>
-      </c>
-      <c r="D145">
-        <v>2</v>
+        <v>129</v>
+      </c>
+      <c r="D145" t="s">
+        <v>155</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>35007</v>
       </c>
       <c r="B146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C146" t="s">
-        <v>131</v>
-      </c>
-      <c r="D146">
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="D146" t="s">
+        <v>155</v>
       </c>
       <c r="E146">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>35008</v>
       </c>
       <c r="B147" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C147" t="s">
-        <v>132</v>
-      </c>
-      <c r="D147">
-        <v>2</v>
+        <v>131</v>
+      </c>
+      <c r="D147" t="s">
+        <v>160</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>35009</v>
       </c>
       <c r="B148" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C148" t="s">
-        <v>133</v>
-      </c>
-      <c r="D148">
-        <v>2</v>
+        <v>132</v>
+      </c>
+      <c r="D148" t="s">
+        <v>148</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>35010</v>
       </c>
       <c r="B149" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C149" t="s">
-        <v>134</v>
-      </c>
-      <c r="D149">
-        <v>2</v>
+        <v>133</v>
+      </c>
+      <c r="D149" t="s">
+        <v>155</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>35011</v>
       </c>
       <c r="B150" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C150" t="s">
-        <v>135</v>
-      </c>
-      <c r="D150">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="D150" t="s">
+        <v>155</v>
       </c>
       <c r="E150">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>35012</v>
       </c>
       <c r="B151" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C151" t="s">
-        <v>136</v>
-      </c>
-      <c r="D151">
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="D151" t="s">
+        <v>155</v>
       </c>
       <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
         <v>2</v>
       </c>
     </row>

--- a/db/tablas_procesadas/Detalle_materia.xlsx
+++ b/db/tablas_procesadas/Detalle_materia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5866886-BE38-4775-8627-D928D810CF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D6F43F-3F9A-46ED-87DC-5598D0B85593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="7170" windowWidth="28785" windowHeight="15345" xr2:uid="{9645E043-A915-45BA-A74B-6A06D7338E21}"/>
+    <workbookView xWindow="9000" yWindow="4515" windowWidth="28785" windowHeight="15345" xr2:uid="{9645E043-A915-45BA-A74B-6A06D7338E21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="246">
-  <si>
-    <t>requisito_id</t>
-  </si>
-  <si>
-    <t>materia_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="129">
   <si>
     <t>CI-IC-001</t>
   </si>
@@ -258,9 +252,6 @@
     <t>DM-IMC-003</t>
   </si>
   <si>
-    <t>AR-IMC-003</t>
-  </si>
-  <si>
     <t>ANM-IMC-002</t>
   </si>
   <si>
@@ -333,390 +324,6 @@
     <t>AM-INC-003</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>C37</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>C43</t>
-  </si>
-  <si>
-    <t>C44</t>
-  </si>
-  <si>
-    <t>C45</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>C50</t>
-  </si>
-  <si>
-    <t>C51</t>
-  </si>
-  <si>
-    <t>C52</t>
-  </si>
-  <si>
-    <t>C53</t>
-  </si>
-  <si>
-    <t>C54</t>
-  </si>
-  <si>
-    <t>C56</t>
-  </si>
-  <si>
-    <t>C57</t>
-  </si>
-  <si>
-    <t>C58</t>
-  </si>
-  <si>
-    <t>C59</t>
-  </si>
-  <si>
-    <t>C60</t>
-  </si>
-  <si>
-    <t>C61</t>
-  </si>
-  <si>
-    <t>C63</t>
-  </si>
-  <si>
-    <t>C64</t>
-  </si>
-  <si>
-    <t>C65</t>
-  </si>
-  <si>
-    <t>C66</t>
-  </si>
-  <si>
-    <t>C67</t>
-  </si>
-  <si>
-    <t>C68</t>
-  </si>
-  <si>
-    <t>C70</t>
-  </si>
-  <si>
-    <t>C71</t>
-  </si>
-  <si>
-    <t>C72</t>
-  </si>
-  <si>
-    <t>C73</t>
-  </si>
-  <si>
-    <t>C74</t>
-  </si>
-  <si>
-    <t>C75</t>
-  </si>
-  <si>
-    <t>C76</t>
-  </si>
-  <si>
-    <t>C77</t>
-  </si>
-  <si>
-    <t>C78</t>
-  </si>
-  <si>
-    <t>C79</t>
-  </si>
-  <si>
-    <t>C82</t>
-  </si>
-  <si>
-    <t>C83</t>
-  </si>
-  <si>
-    <t>C84</t>
-  </si>
-  <si>
-    <t>C85</t>
-  </si>
-  <si>
-    <t>C88</t>
-  </si>
-  <si>
-    <t>C89</t>
-  </si>
-  <si>
-    <t>C90</t>
-  </si>
-  <si>
-    <t>C91</t>
-  </si>
-  <si>
-    <t>C92</t>
-  </si>
-  <si>
-    <t>C93</t>
-  </si>
-  <si>
-    <t>C94</t>
-  </si>
-  <si>
-    <t>C95</t>
-  </si>
-  <si>
-    <t>C96</t>
-  </si>
-  <si>
-    <t>C97</t>
-  </si>
-  <si>
-    <t>C98</t>
-  </si>
-  <si>
-    <t>C99</t>
-  </si>
-  <si>
-    <t>C100</t>
-  </si>
-  <si>
-    <t>C101</t>
-  </si>
-  <si>
-    <t>C104</t>
-  </si>
-  <si>
-    <t>C105</t>
-  </si>
-  <si>
-    <t>C106</t>
-  </si>
-  <si>
-    <t>C107</t>
-  </si>
-  <si>
-    <t>C108</t>
-  </si>
-  <si>
-    <t>C109</t>
-  </si>
-  <si>
-    <t>C111</t>
-  </si>
-  <si>
-    <t>C112</t>
-  </si>
-  <si>
-    <t>C113</t>
-  </si>
-  <si>
-    <t>C114</t>
-  </si>
-  <si>
-    <t>C115</t>
-  </si>
-  <si>
-    <t>C118</t>
-  </si>
-  <si>
-    <t>C119</t>
-  </si>
-  <si>
-    <t>C120</t>
-  </si>
-  <si>
-    <t>C121</t>
-  </si>
-  <si>
-    <t>C122</t>
-  </si>
-  <si>
-    <t>C124</t>
-  </si>
-  <si>
-    <t>C125</t>
-  </si>
-  <si>
-    <t>C126</t>
-  </si>
-  <si>
-    <t>C127</t>
-  </si>
-  <si>
-    <t>C128</t>
-  </si>
-  <si>
-    <t>C129</t>
-  </si>
-  <si>
-    <t>C132</t>
-  </si>
-  <si>
-    <t>C133</t>
-  </si>
-  <si>
-    <t>C134</t>
-  </si>
-  <si>
-    <t>C135</t>
-  </si>
-  <si>
-    <t>C139</t>
-  </si>
-  <si>
-    <t>C140</t>
-  </si>
-  <si>
-    <t>C141</t>
-  </si>
-  <si>
-    <t>C142</t>
-  </si>
-  <si>
-    <t>C143</t>
-  </si>
-  <si>
-    <t>C144</t>
-  </si>
-  <si>
-    <t>C145</t>
-  </si>
-  <si>
-    <t>INO</t>
-  </si>
-  <si>
-    <t>OA</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>3°Ini, 1°Inv</t>
   </si>
   <si>
@@ -772,6 +379,48 @@
   </si>
   <si>
     <t>curso</t>
+  </si>
+  <si>
+    <t>grupos</t>
+  </si>
+  <si>
+    <t>Conjunto</t>
+  </si>
+  <si>
+    <t>Conjunto1</t>
+  </si>
+  <si>
+    <t>Conjunto2</t>
+  </si>
+  <si>
+    <t>Conjunto3</t>
+  </si>
+  <si>
+    <t>Conjunto4</t>
+  </si>
+  <si>
+    <t>id_materia</t>
+  </si>
+  <si>
+    <t>INOG</t>
+  </si>
+  <si>
+    <t>INOS</t>
+  </si>
+  <si>
+    <t>OAG</t>
+  </si>
+  <si>
+    <t>OAS</t>
+  </si>
+  <si>
+    <t>OBG</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>ARM-IMC-003</t>
   </si>
 </sst>
 </file>
@@ -813,8 +462,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1132,1293 +782,1293 @@
   <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>96</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
+        <v>93</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>241</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="B70" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="C70" t="s">
-        <v>237</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>230</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>171</v>
+        <v>39</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>174</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>179</v>
+        <v>47</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C83" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C85" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="C86" t="s">
-        <v>235</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>242</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C89" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="B91" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C91" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C92" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C93" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="C99" t="s">
-        <v>239</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="B101" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C101" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C102" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C103" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="B104" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C104" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="B105" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C105" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="B106" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C106" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C107" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C108" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>206</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C109" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="B110" t="s">
-        <v>229</v>
+        <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>208</v>
+        <v>66</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C111" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C112" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>210</v>
+        <v>68</v>
       </c>
       <c r="B113" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C113" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="B114" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C114" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>243</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="B116" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="B117" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
@@ -2426,101 +2076,101 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C118" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="B119" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C119" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="C120" t="s">
-        <v>224</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="C121" t="s">
-        <v>224</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>221</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="C124" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="C125" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="B126" t="s">
-        <v>229</v>
+        <v>120</v>
       </c>
       <c r="C126" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
